--- a/examples/excel/charts/charts-waterfall.xlsx
+++ b/examples/excel/charts/charts-waterfall.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Waterfall Fundamentals" sheetId="2" r:id="R6ea00c71bd424f9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Waterfall Styling" sheetId="3" r:id="Rab496793acc94349"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Waterfall Labels &amp; Axis" sheetId="4" r:id="R7cd2975a1b0a4fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Waterfall Advanced" sheetId="5" r:id="R8c3fe5bc0e8a4f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Waterfall Fundamentals" sheetId="2" r:id="Re1ae9822dda24be5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Waterfall Styling" sheetId="3" r:id="R14f9fc5ec10a4776"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Waterfall Labels &amp; Axis" sheetId="4" r:id="R6cf009decd814f13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Waterfall Advanced" sheetId="5" r:id="R4fe8f184fd2642d5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3734,7 +3734,15 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
@@ -4310,7 +4318,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1112aedac2ac4d6b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re69e483397f740fa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4340,7 +4348,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdc1878a68866436c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2beb6febecd44cd0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4370,7 +4378,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcadc0a09b7824ab9"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R999a8b7cbc9c4fdf"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4400,7 +4408,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R40cd5aca52d84722"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R94cc9525d78646f0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4435,7 +4443,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1374194097348c5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1420a865627c4883"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4465,7 +4473,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Radfae62e15e1404e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfab3be3895a140b4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4495,7 +4503,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R19b68aadd7a4465e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc846068081734003"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4525,7 +4533,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfd25671f83644739"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f734ac6f34b46f3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4560,7 +4568,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R04d4f3e0d8964196"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd26b1af902ba4fc9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4590,7 +4598,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R84ec75fd5b584758"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8cb0ab4f7fec4a86"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4620,7 +4628,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R06e510419c8e45c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re9a2021858e141ee"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4650,7 +4658,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74b6799dd8224a8d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R37fa6a24d9134217"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4685,7 +4693,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R221b39428c294512"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R909ecfaaf3984202"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4715,7 +4723,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R56aa6dab89d3492c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redb935a9c2634f4c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4745,7 +4753,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4a1c93990b474b0b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdcffbc66f52c43ab"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4775,7 +4783,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R60e86529f39a4247"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R01d0addf689b4f3e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4784,30 +4792,139 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73a21d18207f44e9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3774d3efda4a4d26"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7ef73dd984341e8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R645daf0465c34a53"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra17e4c94af8043cc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5014475b010c4ed7"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab1d207c7c764b1f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf6542366f374bdd"/>
 </x:worksheet>
 </file>